--- a/analyst/Tracy/rmonize/data_proc_elem/DPE_BGS98_TRACY.xlsx
+++ b/analyst/Tracy/rmonize/data_proc_elem/DPE_BGS98_TRACY.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\use-cases-harmonisation\analyst\Tracy\rmonize\data_proc_elem\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\analyst\Tracy\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F91D79-12AE-481F-A912-D149911E067C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC94B63C-67D7-4CAC-A903-92B5FC02B122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="175">
   <si>
     <t>index</t>
   </si>
@@ -511,9 +511,6 @@
   </si>
   <si>
     <t>SDisced97z</t>
-  </si>
-  <si>
-    <t>recode(1=0;2=1;3=2;4=3;5=5;6=6;7=8;)</t>
   </si>
   <si>
     <t>(1.5 * (KAmet31 + KAmet32))+ (3 * (KAmet41 + KAmet42)) + (6 * (KAmet51 + KAmet52)) / 7</t>
@@ -540,14 +537,32 @@
     <t>RCz3C;RCz4C;RCzC</t>
   </si>
   <si>
-    <t>recode(1=1;2=2;3=3;4=3;5=4;6=5;7=6;)</t>
+    <t>proximate</t>
+  </si>
+  <si>
+    <t>FS: I saw in the DD that this is coded the other way round. Can you double check that. Seems unusual</t>
+  </si>
+  <si>
+    <t>FS: Is that really the name of the variable?</t>
+  </si>
+  <si>
+    <t>ID0339</t>
+  </si>
+  <si>
+    <t>recode(1=1;2=3;3=3;4=3;5=4;6=6;7=7;)</t>
+  </si>
+  <si>
+    <t>FS: a bit unclear from descriptions</t>
+  </si>
+  <si>
+    <t>recode(1=3;2=3;3=2;4=2;5=1;)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -582,6 +597,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -603,7 +626,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -629,9 +652,13 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -647,9 +674,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -687,9 +714,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -722,26 +749,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -774,26 +784,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -968,7 +961,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K61"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="59.140625" bestFit="1" customWidth="1"/>
@@ -1027,8 +1020,8 @@
       <c r="D2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="8" t="s">
-        <v>11</v>
+      <c r="F2" s="13" t="s">
+        <v>171</v>
       </c>
       <c r="G2" s="10" t="s">
         <v>134</v>
@@ -1117,14 +1110,17 @@
       <c r="G5" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="H5" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>141</v>
+      <c r="H5" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="J5" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -1146,7 +1142,7 @@
         <v>140</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
@@ -1174,8 +1170,8 @@
       <c r="G7" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>169</v>
+      <c r="H7" s="13" t="s">
+        <v>174</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
@@ -1225,16 +1221,16 @@
         <v>13</v>
       </c>
       <c r="F9" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="I9" s="14" t="s">
         <v>165</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>166</v>
       </c>
       <c r="J9" s="11" t="s">
         <v>135</v>
@@ -1302,7 +1298,7 @@
       </c>
       <c r="E12" s="3"/>
       <c r="F12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>140</v>
@@ -1311,10 +1307,10 @@
         <v>146</v>
       </c>
       <c r="I12" s="3"/>
-      <c r="J12" s="3" t="s">
+      <c r="J12" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="K12" s="3" t="s">
+      <c r="K12" s="13" t="s">
         <v>141</v>
       </c>
     </row>
@@ -1395,8 +1391,8 @@
       <c r="J15" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="K15" s="8" t="s">
-        <v>141</v>
+      <c r="K15" s="13" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -2400,8 +2396,11 @@
       <c r="G57" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="H57" s="8" t="s">
+      <c r="H57" s="13" t="s">
         <v>156</v>
+      </c>
+      <c r="I57" s="13" t="s">
+        <v>169</v>
       </c>
       <c r="J57" s="12" t="s">
         <v>135</v>
@@ -2492,7 +2491,7 @@
       <c r="D61" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F61" s="8" t="s">
+      <c r="F61" s="13" t="s">
         <v>132</v>
       </c>
       <c r="G61" s="8" t="s">
@@ -2500,6 +2499,9 @@
       </c>
       <c r="H61" s="8" t="s">
         <v>138</v>
+      </c>
+      <c r="I61" s="13" t="s">
+        <v>170</v>
       </c>
       <c r="J61" s="11" t="s">
         <v>135</v>

--- a/analyst/Tracy/rmonize/data_proc_elem/DPE_BGS98_TRACY.xlsx
+++ b/analyst/Tracy/rmonize/data_proc_elem/DPE_BGS98_TRACY.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\analyst\Tracy\rmonize\data_proc_elem\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\use-cases-harmonisation\analyst\Tracy\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC94B63C-67D7-4CAC-A903-92B5FC02B122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CA5BD93-08DF-4543-B4CE-E309AC13AB5C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="169">
   <si>
     <t>index</t>
   </si>
@@ -462,18 +462,12 @@
     <t>SDerwerbB</t>
   </si>
   <si>
-    <t>recode(1=5;2=2;3=2;4=1;5=7;6=6;)</t>
-  </si>
-  <si>
     <t>(RCz3C*5)+(RCz4C *5)+(RCzC*1)</t>
   </si>
   <si>
     <t>KHdiab12p</t>
   </si>
   <si>
-    <t>recode(1=1;2=0;)</t>
-  </si>
-  <si>
     <t>KHhyp12p</t>
   </si>
   <si>
@@ -495,9 +489,6 @@
     <t>SEmens2</t>
   </si>
   <si>
-    <t>recode(1=0;2=1;)</t>
-  </si>
-  <si>
     <t>incompatible</t>
   </si>
   <si>
@@ -516,53 +507,38 @@
     <t>(1.5 * (KAmet31 + KAmet32))+ (3 * (KAmet41 + KAmet42)) + (6 * (KAmet51 + KAmet52)) / 7</t>
   </si>
   <si>
-    <t>case_when</t>
-  </si>
-  <si>
-    <t>MIstaat_m1;MIstaat_m2</t>
-  </si>
-  <si>
-    <t># if nationality is German then map to 1
-# if nationality is Other then map to 0
-# everything else (missing or unexpected values</t>
-  </si>
-  <si>
-    <t>case_when(
-  MIstaat_m1 == 1 ~ 1,
-  MIstaat_m2 == 1 ~ 0,
-  TRUE ~ NA_integer_
-)</t>
-  </si>
-  <si>
     <t>RCz3C;RCz4C;RCzC</t>
   </si>
   <si>
     <t>proximate</t>
   </si>
   <si>
-    <t>FS: I saw in the DD that this is coded the other way round. Can you double check that. Seems unusual</t>
-  </si>
-  <si>
-    <t>FS: Is that really the name of the variable?</t>
-  </si>
-  <si>
     <t>ID0339</t>
   </si>
   <si>
-    <t>recode(1=1;2=3;3=3;4=3;5=4;6=6;7=7;)</t>
-  </si>
-  <si>
-    <t>FS: a bit unclear from descriptions</t>
-  </si>
-  <si>
-    <t>recode(1=3;2=3;3=2;4=2;5=1;)</t>
+    <t>recode(1=1;2=3;3=3;4=3;5=4;6=6;7=7;8:8)</t>
+  </si>
+  <si>
+    <t>recode(1=3;2=3;3=2;4=2;5=1)</t>
+  </si>
+  <si>
+    <t>recode(1=5;2=2;3=2;4=1;5=7;6=6)</t>
+  </si>
+  <si>
+    <t>recode(1=1;2=0)</t>
+  </si>
+  <si>
+    <t>MIausl</t>
+  </si>
+  <si>
+    <t>This is taken from DEGS1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -605,6 +581,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -626,7 +609,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -652,13 +635,14 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -674,9 +658,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -714,9 +698,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -749,9 +733,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -784,9 +785,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -961,7 +979,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K61"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="59.140625" bestFit="1" customWidth="1"/>
@@ -1020,8 +1038,8 @@
       <c r="D2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="13" t="s">
-        <v>171</v>
+      <c r="F2" s="8" t="s">
+        <v>162</v>
       </c>
       <c r="G2" s="10" t="s">
         <v>134</v>
@@ -1105,22 +1123,20 @@
         <v>13</v>
       </c>
       <c r="F5" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="I5" s="14"/>
+      <c r="J5" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="K5" s="8" t="s">
         <v>161</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="I5" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="J5" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="K5" s="13" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -1142,7 +1158,7 @@
         <v>140</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
@@ -1152,32 +1168,29 @@
         <v>141</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3" t="s">
+    <row r="7" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3" t="s">
+      <c r="D7" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3" t="s">
+      <c r="G7" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="J7" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="K7" s="8" t="s">
         <v>141</v>
       </c>
     </row>
@@ -1197,10 +1210,10 @@
         <v>144</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">
@@ -1210,7 +1223,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="8" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="8" t="s">
         <v>27</v>
       </c>
@@ -1220,18 +1233,16 @@
       <c r="D9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>164</v>
+      <c r="F9" s="15" t="s">
+        <v>167</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="H9" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="I9" s="14" t="s">
-        <v>165</v>
-      </c>
+      <c r="I9" s="13"/>
       <c r="J9" s="11" t="s">
         <v>135</v>
       </c>
@@ -1250,16 +1261,16 @@
         <v>18</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -1273,16 +1284,16 @@
         <v>18</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1298,19 +1309,19 @@
       </c>
       <c r="E12" s="3"/>
       <c r="F12" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>140</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I12" s="3"/>
-      <c r="J12" s="13" t="s">
+      <c r="J12" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="K12" s="13" t="s">
+      <c r="K12" s="8" t="s">
         <v>141</v>
       </c>
     </row>
@@ -1327,7 +1338,7 @@
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>138</v>
@@ -1357,16 +1368,16 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -1380,19 +1391,19 @@
         <v>13</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="K15" s="13" t="s">
-        <v>168</v>
+        <v>152</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1407,16 +1418,16 @@
       </c>
       <c r="F16" s="3"/>
       <c r="G16" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H16" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
@@ -1431,17 +1442,17 @@
       </c>
       <c r="F17" s="3"/>
       <c r="G17" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H17" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
@@ -1456,17 +1467,17 @@
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
@@ -1481,17 +1492,17 @@
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
@@ -1505,13 +1516,13 @@
         <v>13</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="s">
@@ -1532,13 +1543,13 @@
         <v>13</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="s">
@@ -1559,13 +1570,13 @@
         <v>13</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>135</v>
@@ -1585,13 +1596,13 @@
         <v>13</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G23" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="J23" t="s">
         <v>135</v>
@@ -1611,16 +1622,16 @@
         <v>13</v>
       </c>
       <c r="G24" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H24" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
@@ -1634,16 +1645,16 @@
         <v>13</v>
       </c>
       <c r="G25" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H25" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26" spans="2:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -1657,16 +1668,16 @@
         <v>13</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
@@ -1680,16 +1691,16 @@
         <v>13</v>
       </c>
       <c r="G27" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H27" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
@@ -1703,16 +1714,16 @@
         <v>13</v>
       </c>
       <c r="G28" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H28" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
@@ -1726,16 +1737,16 @@
         <v>13</v>
       </c>
       <c r="G29" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H29" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
@@ -1749,16 +1760,16 @@
         <v>13</v>
       </c>
       <c r="G30" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H30" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
@@ -1772,16 +1783,16 @@
         <v>13</v>
       </c>
       <c r="G31" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H31" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
@@ -1795,16 +1806,16 @@
         <v>13</v>
       </c>
       <c r="G32" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H32" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
@@ -1818,16 +1829,16 @@
         <v>13</v>
       </c>
       <c r="G33" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H33" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
@@ -1841,16 +1852,16 @@
         <v>13</v>
       </c>
       <c r="G34" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H34" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="35" spans="2:11" s="9" customFormat="1" x14ac:dyDescent="0.25">
@@ -1864,16 +1875,16 @@
         <v>13</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K35" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
@@ -1887,17 +1898,17 @@
         <v>13</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I36" s="9"/>
       <c r="J36" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K36" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
@@ -1911,17 +1922,17 @@
         <v>18</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I37" s="9"/>
       <c r="J37" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K37" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
@@ -1935,17 +1946,17 @@
         <v>13</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I38" s="9"/>
       <c r="J38" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K38" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
@@ -1959,17 +1970,17 @@
         <v>18</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I39" s="9"/>
       <c r="J39" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K39" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
@@ -1983,17 +1994,17 @@
         <v>13</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I40" s="9"/>
       <c r="J40" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K40" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
@@ -2007,17 +2018,17 @@
         <v>18</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I41" s="9"/>
       <c r="J41" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K41" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
@@ -2031,17 +2042,17 @@
         <v>13</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I42" s="9"/>
       <c r="J42" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K42" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.25">
@@ -2055,17 +2066,17 @@
         <v>18</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I43" s="9"/>
       <c r="J43" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K43" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
@@ -2079,17 +2090,17 @@
         <v>13</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I44" s="9"/>
       <c r="J44" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K44" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
@@ -2103,17 +2114,17 @@
         <v>18</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K45" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
@@ -2127,17 +2138,17 @@
         <v>13</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I46" s="9"/>
       <c r="J46" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K46" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
@@ -2151,17 +2162,17 @@
         <v>18</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I47" s="9"/>
       <c r="J47" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K47" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
@@ -2175,17 +2186,17 @@
         <v>13</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I48" s="9"/>
       <c r="J48" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K48" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.25">
@@ -2199,17 +2210,17 @@
         <v>18</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K49" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
@@ -2223,17 +2234,17 @@
         <v>13</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I50" s="9"/>
       <c r="J50" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K50" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
@@ -2247,17 +2258,17 @@
         <v>18</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I51" s="9"/>
       <c r="J51" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K51" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.25">
@@ -2271,17 +2282,17 @@
         <v>13</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I52" s="9"/>
       <c r="J52" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K52" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.25">
@@ -2295,17 +2306,17 @@
         <v>18</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I53" s="9"/>
       <c r="J53" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K53" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.25">
@@ -2319,17 +2330,17 @@
         <v>13</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I54" s="9"/>
       <c r="J54" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K54" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
@@ -2343,17 +2354,17 @@
         <v>121</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K55" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
@@ -2367,17 +2378,17 @@
         <v>18</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I56" s="9"/>
       <c r="J56" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K56" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="57" spans="2:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -2391,17 +2402,15 @@
         <v>13</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G57" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H57" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="I57" s="13" t="s">
-        <v>169</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="H57" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="I57" s="14"/>
       <c r="J57" s="12" t="s">
         <v>135</v>
       </c>
@@ -2420,17 +2429,17 @@
         <v>18</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I58" s="9"/>
       <c r="J58" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K58" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.25">
@@ -2444,17 +2453,17 @@
         <v>13</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I59" s="9"/>
       <c r="J59" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K59" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
@@ -2468,17 +2477,17 @@
         <v>13</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H60" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I60" s="9"/>
       <c r="J60" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K60" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="61" spans="2:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -2491,7 +2500,7 @@
       <c r="D61" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F61" s="13" t="s">
+      <c r="F61" s="8" t="s">
         <v>132</v>
       </c>
       <c r="G61" s="8" t="s">
@@ -2500,8 +2509,8 @@
       <c r="H61" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="I61" s="13" t="s">
-        <v>170</v>
+      <c r="I61" s="8" t="s">
+        <v>168</v>
       </c>
       <c r="J61" s="11" t="s">
         <v>135</v>

--- a/analyst/Tracy/rmonize/data_proc_elem/DPE_BGS98_TRACY.xlsx
+++ b/analyst/Tracy/rmonize/data_proc_elem/DPE_BGS98_TRACY.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\use-cases-harmonisation\analyst\Tracy\rmonize\data_proc_elem\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\analyst\Tracy\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CA5BD93-08DF-4543-B4CE-E309AC13AB5C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C247ABF5-5707-44D7-85FC-DFEDC71E2980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -456,9 +456,6 @@
     <t>RCstatD</t>
   </si>
   <si>
-    <t>KAmet31;KAmet32; KAmet41;KAmet42; KAmet51;KAmet52</t>
-  </si>
-  <si>
     <t>SDerwerbB</t>
   </si>
   <si>
@@ -516,9 +513,6 @@
     <t>ID0339</t>
   </si>
   <si>
-    <t>recode(1=1;2=3;3=3;4=3;5=4;6=6;7=7;8:8)</t>
-  </si>
-  <si>
     <t>recode(1=3;2=3;3=2;4=2;5=1)</t>
   </si>
   <si>
@@ -532,6 +526,12 @@
   </si>
   <si>
     <t>This is taken from DEGS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">recode(1=1;2=2;3=3;4=3;5=4;6=6;7=7;8=8) </t>
+  </si>
+  <si>
+    <t>KAmet31;KAmet32;KAmet41;KAmet42;KAmet51;KAmet52</t>
   </si>
 </sst>
 </file>
@@ -642,7 +642,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -658,9 +658,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -698,9 +698,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -733,26 +733,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -785,26 +768,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -979,7 +945,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K61"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="59.140625" bestFit="1" customWidth="1"/>
@@ -1039,7 +1005,7 @@
         <v>13</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G2" s="10" t="s">
         <v>134</v>
@@ -1123,20 +1089,20 @@
         <v>13</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="I5" s="14"/>
       <c r="J5" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -1152,13 +1118,13 @@
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="4" t="s">
-        <v>143</v>
+        <v>168</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>140</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
@@ -1182,10 +1148,10 @@
         <v>142</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J7" s="8" t="s">
         <v>135</v>
@@ -1207,13 +1173,13 @@
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">
@@ -1234,13 +1200,13 @@
         <v>13</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I9" s="13"/>
       <c r="J9" s="11" t="s">
@@ -1261,16 +1227,16 @@
         <v>18</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -1284,16 +1250,16 @@
         <v>18</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1309,13 +1275,13 @@
       </c>
       <c r="E12" s="3"/>
       <c r="F12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>140</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="8" t="s">
@@ -1338,7 +1304,7 @@
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>138</v>
@@ -1368,16 +1334,16 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -1391,19 +1357,19 @@
         <v>13</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1418,16 +1384,16 @@
       </c>
       <c r="F16" s="3"/>
       <c r="G16" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H16" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
@@ -1442,17 +1408,17 @@
       </c>
       <c r="F17" s="3"/>
       <c r="G17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
@@ -1467,17 +1433,17 @@
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
@@ -1492,17 +1458,17 @@
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
@@ -1516,13 +1482,13 @@
         <v>13</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="s">
@@ -1543,13 +1509,13 @@
         <v>13</v>
       </c>
       <c r="F21" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="H21" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="s">
@@ -1570,13 +1536,13 @@
         <v>13</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>135</v>
@@ -1596,13 +1562,13 @@
         <v>13</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G23" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J23" t="s">
         <v>135</v>
@@ -1622,16 +1588,16 @@
         <v>13</v>
       </c>
       <c r="G24" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H24" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
@@ -1645,16 +1611,16 @@
         <v>13</v>
       </c>
       <c r="G25" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H25" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26" spans="2:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -1668,16 +1634,16 @@
         <v>13</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
@@ -1691,16 +1657,16 @@
         <v>13</v>
       </c>
       <c r="G27" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H27" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
@@ -1714,16 +1680,16 @@
         <v>13</v>
       </c>
       <c r="G28" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H28" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
@@ -1737,16 +1703,16 @@
         <v>13</v>
       </c>
       <c r="G29" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H29" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
@@ -1760,16 +1726,16 @@
         <v>13</v>
       </c>
       <c r="G30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
@@ -1783,16 +1749,16 @@
         <v>13</v>
       </c>
       <c r="G31" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H31" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
@@ -1806,16 +1772,16 @@
         <v>13</v>
       </c>
       <c r="G32" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H32" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
@@ -1829,16 +1795,16 @@
         <v>13</v>
       </c>
       <c r="G33" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H33" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
@@ -1852,16 +1818,16 @@
         <v>13</v>
       </c>
       <c r="G34" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H34" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35" spans="2:11" s="9" customFormat="1" x14ac:dyDescent="0.25">
@@ -1875,16 +1841,16 @@
         <v>13</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K35" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
@@ -1898,17 +1864,17 @@
         <v>13</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I36" s="9"/>
       <c r="J36" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K36" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
@@ -1922,17 +1888,17 @@
         <v>18</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I37" s="9"/>
       <c r="J37" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K37" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
@@ -1946,17 +1912,17 @@
         <v>13</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I38" s="9"/>
       <c r="J38" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K38" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
@@ -1970,17 +1936,17 @@
         <v>18</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I39" s="9"/>
       <c r="J39" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K39" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
@@ -1994,17 +1960,17 @@
         <v>13</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I40" s="9"/>
       <c r="J40" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K40" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
@@ -2018,17 +1984,17 @@
         <v>18</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I41" s="9"/>
       <c r="J41" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K41" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
@@ -2042,17 +2008,17 @@
         <v>13</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I42" s="9"/>
       <c r="J42" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K42" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.25">
@@ -2066,17 +2032,17 @@
         <v>18</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I43" s="9"/>
       <c r="J43" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K43" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
@@ -2090,17 +2056,17 @@
         <v>13</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I44" s="9"/>
       <c r="J44" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K44" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
@@ -2114,17 +2080,17 @@
         <v>18</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K45" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
@@ -2138,17 +2104,17 @@
         <v>13</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I46" s="9"/>
       <c r="J46" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K46" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
@@ -2162,17 +2128,17 @@
         <v>18</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I47" s="9"/>
       <c r="J47" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K47" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
@@ -2186,17 +2152,17 @@
         <v>13</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I48" s="9"/>
       <c r="J48" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K48" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.25">
@@ -2210,17 +2176,17 @@
         <v>18</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K49" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
@@ -2234,17 +2200,17 @@
         <v>13</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I50" s="9"/>
       <c r="J50" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K50" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
@@ -2258,17 +2224,17 @@
         <v>18</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I51" s="9"/>
       <c r="J51" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K51" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.25">
@@ -2282,17 +2248,17 @@
         <v>13</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I52" s="9"/>
       <c r="J52" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K52" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.25">
@@ -2306,17 +2272,17 @@
         <v>18</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I53" s="9"/>
       <c r="J53" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K53" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.25">
@@ -2330,17 +2296,17 @@
         <v>13</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I54" s="9"/>
       <c r="J54" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K54" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
@@ -2354,17 +2320,17 @@
         <v>121</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K55" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
@@ -2378,17 +2344,17 @@
         <v>18</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I56" s="9"/>
       <c r="J56" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K56" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="57" spans="2:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -2402,13 +2368,13 @@
         <v>13</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G57" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I57" s="14"/>
       <c r="J57" s="12" t="s">
@@ -2429,17 +2395,17 @@
         <v>18</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I58" s="9"/>
       <c r="J58" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K58" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.25">
@@ -2453,17 +2419,17 @@
         <v>13</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I59" s="9"/>
       <c r="J59" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K59" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
@@ -2477,17 +2443,17 @@
         <v>13</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H60" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I60" s="9"/>
       <c r="J60" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K60" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="61" spans="2:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -2510,7 +2476,7 @@
         <v>138</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J61" s="11" t="s">
         <v>135</v>

--- a/analyst/Tracy/rmonize/data_proc_elem/DPE_BGS98_TRACY.xlsx
+++ b/analyst/Tracy/rmonize/data_proc_elem/DPE_BGS98_TRACY.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\analyst\Tracy\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C247ABF5-5707-44D7-85FC-DFEDC71E2980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A9FD61C-51C5-4C75-A699-51570DC26C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29220" yWindow="3615" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="171">
   <si>
     <t>index</t>
   </si>
@@ -522,9 +522,6 @@
     <t>recode(1=1;2=0)</t>
   </si>
   <si>
-    <t>MIausl</t>
-  </si>
-  <si>
     <t>This is taken from DEGS1</t>
   </si>
   <si>
@@ -532,6 +529,17 @@
   </si>
   <si>
     <t>KAmet31;KAmet32;KAmet41;KAmet42;KAmet51;KAmet52</t>
+  </si>
+  <si>
+    <t>case_when</t>
+  </si>
+  <si>
+    <t>case_when(is.na(MIlandB) ~ 1,
+          is.na(MIstaat_m1) ~ 1,
+          TRUE ~ 0)</t>
+  </si>
+  <si>
+    <t>MIlandB;MIstaat_m1</t>
   </si>
 </sst>
 </file>
@@ -609,7 +617,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -639,7 +647,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1095,7 +1102,7 @@
         <v>147</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I5" s="14"/>
       <c r="J5" s="8" t="s">
@@ -1118,7 +1125,7 @@
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>140</v>
@@ -1189,7 +1196,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" s="8" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B9" s="8" t="s">
         <v>27</v>
       </c>
@@ -1199,14 +1206,14 @@
       <c r="D9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="15" t="s">
-        <v>165</v>
+      <c r="F9" t="s">
+        <v>170</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>169</v>
       </c>
       <c r="I9" s="13"/>
       <c r="J9" s="11" t="s">
@@ -2476,7 +2483,7 @@
         <v>138</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J61" s="11" t="s">
         <v>135</v>
